--- a/jogos_2024-11-29.xlsx
+++ b/jogos_2024-11-29.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['75']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45625.39583333334</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['75']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45625.39583333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.75</v>
+        <v>2.51</v>
       </c>
       <c r="M13" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>1.53</v>
+        <v>2.61</v>
       </c>
       <c r="O13" t="n">
-        <v>6.5</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="R13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.4</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.38</v>
-      </c>
       <c r="X13" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="Y13" t="n">
         <v>1.95</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['49']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['19', '37']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>2.09</v>
+        <v>1.43</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="AI13" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.36</v>
+        <v>1.97</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45625.5</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.51</v>
+        <v>5.75</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="N14" t="n">
-        <v>2.61</v>
+        <v>1.53</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="P14" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="T14" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X14" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="Y14" t="n">
         <v>1.95</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['49']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19', '37']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.43</v>
+        <v>2.09</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.34</v>
+        <v>1.11</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.97</v>
+        <v>1.36</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45625.5</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,109 +2707,109 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.5</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
       <c r="U18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['11', '78']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['25', '31', '69']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.36</v>
       </c>
-      <c r="V18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['25', '43']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['22']</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AI18" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45625.58333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S19" t="n">
         <v>2.55</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>4</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T19" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="V19" t="n">
         <v>1.04</v>
       </c>
       <c r="W19" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="X19" t="n">
-        <v>3.44</v>
+        <v>2.78</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.44</v>
+        <v>3.58</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AC19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.75</v>
       </c>
-      <c r="AD19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['40', '66']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['43']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AI19" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.4</v>
+        <v>2.77</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45625.58333333334</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,16 +2965,16 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="M20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T20" t="n">
         <v>2.8</v>
       </c>
-      <c r="N20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W20" t="n">
         <v>1.29</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.41</v>
-      </c>
       <c r="X20" t="n">
-        <v>2.8</v>
+        <v>3.44</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.6</v>
+        <v>1.97</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.48</v>
+        <v>1.92</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['28', '52', '55']</t>
+          <t>['40', '66']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45625.58333333334</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,22 +3094,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Horn</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6</v>
+        <v>1.91</v>
       </c>
       <c r="M21" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="O21" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="P21" t="n">
         <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
         <v>3.05</v>
       </c>
       <c r="T21" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X21" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Z21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.95</v>
       </c>
-      <c r="AA21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AI21" t="n">
-        <v>3.6</v>
+        <v>1.57</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45625.58333333334</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,22 +3223,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Spartak Vladikavkaz</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -3249,65 +3249,65 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="N22" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB22" t="n">
         <v>1.17</v>
       </c>
-      <c r="M22" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="N22" t="n">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X22" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AC22" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['21', '45+1', '80']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AH22" t="n">
-        <v>4.33</v>
+        <v>2.74</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AJ22" t="n">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45625.58333333334</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,19 +3352,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Adanaspor</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.91</v>
+        <v>1.29</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>4.85</v>
       </c>
       <c r="N23" t="n">
-        <v>3.9</v>
+        <v>8.5</v>
       </c>
       <c r="O23" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>6.75</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U23" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="Z23" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.67</v>
+        <v>2.07</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>['45+6', '61']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.95</v>
+        <v>2.82</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.5</v>
+        <v>4.15</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45625.58333333334</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,22 +3481,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Šibenik</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>6.89</v>
       </c>
       <c r="N24" t="n">
-        <v>6.25</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="P24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X24" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AA24" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AB24" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AI24" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>['6', '47']</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['82']</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45625.58333333334</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z25" t="n">
         <v>1.8</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N25" t="n">
-        <v>4</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y25" t="n">
+      <c r="AA25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>['25', '43']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>['22']</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>2.1</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>['56']</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>2.77</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45625.58333333334</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,91 +3739,91 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spartak Vladikavkaz</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y26" t="n">
         <v>2</v>
       </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M26" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="N26" t="n">
-        <v>8.880000000000001</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U26" t="n">
+      <c r="Z26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.33</v>
       </c>
-      <c r="V26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AC26" t="n">
-        <v>2.34</v>
+        <v>1.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['21', '45+1', '80']</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.06</v>
+        <v>1.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.74</v>
+        <v>1.47</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.34</v>
+        <v>1.73</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.92</v>
+        <v>2.3</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45625.58333333334</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,109 +3868,109 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O27" t="n">
         <v>3</v>
       </c>
-      <c r="I27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T27" t="n">
         <v>3.5</v>
       </c>
-      <c r="P27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.5</v>
-      </c>
       <c r="U27" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="V27" t="n">
         <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="X27" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="Y27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.67</v>
       </c>
-      <c r="Z27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['11', '78']</t>
+          <t>['28', '52', '55']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['25', '31', '69']</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.66</v>
+        <v>1.24</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.67</v>
+        <v>2.63</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45625.58333333334</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,57 +3997,57 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Horn</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Adanaspor</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>6</v>
+      </c>
+      <c r="M28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>6</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q28" t="n">
         <v>2</v>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M28" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="N28" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>6.75</v>
-      </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="T28" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="U28" t="n">
         <v>1.44</v>
@@ -4056,32 +4056,32 @@
         <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X28" t="n">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['45+6', '61']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.05</v>
+        <v>2.45</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.82</v>
+        <v>1.09</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.34</v>
+        <v>3.6</v>
       </c>
       <c r="AJ28" t="n">
-        <v>4.15</v>
+        <v>1.33</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45625.58333333334</v>
@@ -4126,16 +4126,16 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Lafnitz</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M29" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="N29" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD29" t="n">
         <v>2.2</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB29" t="n">
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>['46', '51', '68']</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI29" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>['54']</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ29" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45625.58333333334</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,22 +4255,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lafnitz</t>
+          <t>Šibenik</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="M30" t="n">
-        <v>5.25</v>
+        <v>3.7</v>
       </c>
       <c r="N30" t="n">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="P30" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>3.7</v>
+        <v>2.69</v>
       </c>
       <c r="T30" t="n">
-        <v>2.24</v>
+        <v>3.26</v>
       </c>
       <c r="U30" t="n">
-        <v>1.59</v>
+        <v>1.32</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W30" t="n">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="X30" t="n">
-        <v>4.5</v>
+        <v>2.88</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.63</v>
+        <v>1.6</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.3</v>
+        <v>3.95</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['46', '51', '68']</t>
+          <t>['6', '47']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.6</v>
+        <v>2.04</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45625.58333333334</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,22 +4384,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="M31" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>2.09</v>
+        <v>2.42</v>
       </c>
       <c r="O31" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X31" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA31" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q31" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S31" t="n">
+      <c r="AB31" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD31" t="n">
         <v>2.75</v>
       </c>
-      <c r="T31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD31" t="n">
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>['55', '65', '86']</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI31" t="n">
         <v>1.95</v>
       </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>['26', '68']</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AJ31" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45625.60416666666</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.13</v>
+        <v>3.1</v>
       </c>
       <c r="M32" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="N32" t="n">
-        <v>3.05</v>
+        <v>2.09</v>
       </c>
       <c r="O32" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="P32" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q32" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X32" t="n">
         <v>3.4</v>
       </c>
-      <c r="R32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X32" t="n">
-        <v>4.5</v>
-      </c>
       <c r="Y32" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
+          <t>['26', '68']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>['12', '52', '61']</t>
-        </is>
-      </c>
       <c r="AG32" t="n">
-        <v>1.36</v>
+        <v>1.69</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45625.60416666666</v>
@@ -4771,16 +4771,16 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>3</v>
@@ -4789,7 +4789,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA34" t="n">
         <v>2.55</v>
       </c>
-      <c r="M34" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O34" t="n">
-        <v>3</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X34" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Y34" t="n">
+      <c r="AB34" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z34" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AC34" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['55', '65', '86']</t>
+          <t>['12', '52', '61']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45625.60416666666</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,16 +5029,16 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>AaB</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -5055,65 +5055,65 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.3</v>
+        <v>1.42</v>
       </c>
       <c r="M36" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="N36" t="n">
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="O36" t="n">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="P36" t="n">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
       <c r="Q36" t="n">
+        <v>6</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S36" t="n">
         <v>3.75</v>
       </c>
-      <c r="R36" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.39</v>
-      </c>
       <c r="T36" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="U36" t="n">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="V36" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="X36" t="n">
-        <v>2.7</v>
+        <v>5.75</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.25</v>
+        <v>1.48</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="AA36" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['21', '85']</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.55</v>
+        <v>2.8</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.93</v>
+        <v>1.29</v>
       </c>
       <c r="AJ36" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45625.625</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,16 +5158,16 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AaB</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -5184,65 +5184,65 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.42</v>
+        <v>2.3</v>
       </c>
       <c r="M37" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="N37" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="O37" t="n">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="P37" t="n">
-        <v>2.63</v>
+        <v>1.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="R37" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="S37" t="n">
-        <v>3.75</v>
+        <v>2.39</v>
       </c>
       <c r="T37" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="U37" t="n">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W37" t="n">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="X37" t="n">
-        <v>5.75</v>
+        <v>2.7</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.48</v>
+        <v>2.25</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>['21', '85']</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.8</v>
+        <v>1.55</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.29</v>
+        <v>1.93</v>
       </c>
       <c r="AJ37" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45625.625</v>
@@ -5545,22 +5545,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -5571,65 +5571,65 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.78</v>
+        <v>1.4</v>
       </c>
       <c r="M40" t="n">
-        <v>4.14</v>
+        <v>5.39</v>
       </c>
       <c r="N40" t="n">
-        <v>3.89</v>
+        <v>6.21</v>
       </c>
       <c r="O40" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="P40" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="R40" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="S40" t="n">
-        <v>3.9</v>
+        <v>4.65</v>
       </c>
       <c r="T40" t="n">
-        <v>2.12</v>
+        <v>1.86</v>
       </c>
       <c r="U40" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="V40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AA40" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.73</v>
+        <v>2.01</v>
       </c>
       <c r="AC40" t="n">
         <v>1.47</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>['2', '29']</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -5638,16 +5638,16 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45625.66666666666</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,109 +5674,109 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N41" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X41" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z41" t="n">
         <v>2</v>
       </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>2</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M41" t="n">
-        <v>5.39</v>
-      </c>
-      <c r="N41" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="O41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R41" t="n">
+      <c r="AA41" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>['22']</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
         <v>1.16</v>
       </c>
-      <c r="S41" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="T41" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X41" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>['2', '29']</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AH41" t="n">
-        <v>3</v>
+        <v>2.04</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45625.66666666666</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5818,10 +5818,10 @@
         <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5829,25 +5829,25 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.81</v>
+        <v>2.42</v>
       </c>
       <c r="M42" t="n">
-        <v>3.9</v>
+        <v>3.66</v>
       </c>
       <c r="N42" t="n">
-        <v>3.98</v>
+        <v>2.71</v>
       </c>
       <c r="O42" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="P42" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="R42" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S42" t="n">
         <v>3.35</v>
@@ -5868,7 +5868,7 @@
         <v>4.33</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z42" t="n">
         <v>2.15</v>
@@ -5877,35 +5877,35 @@
         <v>2.7</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['7', '42']</t>
+          <t>['58', '69']</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45625.66666666666</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,22 +5932,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
         <v>2</v>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>3.46</v>
       </c>
       <c r="N43" t="n">
-        <v>2.18</v>
+        <v>2.69</v>
       </c>
       <c r="O43" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P43" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="R43" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T43" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U43" t="n">
         <v>1.48</v>
       </c>
       <c r="V43" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W43" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X43" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['2', '18', '20', '90']</t>
+          <t>['15', '32']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>['39', '84']</t>
+          <t>['45+1', '90+1']</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AI43" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45625.66666666666</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,109 +6061,109 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G44" t="n">
+        <v>4</v>
+      </c>
+      <c r="H44" t="n">
         <v>2</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>3</v>
       </c>
-      <c r="I44" t="n">
-        <v>1</v>
-      </c>
       <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S44" t="n">
         <v>3</v>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M44" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N44" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="O44" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="P44" t="n">
+      <c r="T44" t="n">
         <v>2.45</v>
       </c>
-      <c r="Q44" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S44" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.24</v>
-      </c>
       <c r="U44" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X44" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC44" t="n">
         <v>1.59</v>
       </c>
-      <c r="V44" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X44" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AD44" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>['33', '90+2']</t>
+          <t>['2', '18', '20', '90']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>['13', '25', '45+2']</t>
+          <t>['39', '84']</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>2.3</v>
+        <v>1.49</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AI44" t="n">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45625.66666666666</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,19 +6448,19 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G47" t="n">
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>1</v>
@@ -6474,83 +6474,83 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="M47" t="n">
-        <v>3.53</v>
+        <v>4.14</v>
       </c>
       <c r="N47" t="n">
-        <v>4.52</v>
+        <v>3.89</v>
       </c>
       <c r="O47" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="P47" t="n">
         <v>2.5</v>
       </c>
       <c r="Q47" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X47" t="n">
         <v>5.5</v>
       </c>
-      <c r="R47" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S47" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X47" t="n">
-        <v>4.65</v>
-      </c>
       <c r="Y47" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI47" t="n">
         <v>1.62</v>
       </c>
-      <c r="Z47" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>['27']</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>['90+1']</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AJ47" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45625.66666666666</v>
@@ -6577,25 +6577,25 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -6603,83 +6603,83 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.62</v>
+        <v>4.4</v>
       </c>
       <c r="M48" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="N48" t="n">
-        <v>4.6</v>
+        <v>1.71</v>
       </c>
       <c r="O48" t="n">
-        <v>2.22</v>
+        <v>4.75</v>
       </c>
       <c r="P48" t="n">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.85</v>
+        <v>2.05</v>
       </c>
       <c r="R48" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S48" t="n">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="T48" t="n">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="U48" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="V48" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W48" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X48" t="n">
-        <v>3.65</v>
+        <v>5.01</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="Z48" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.73</v>
+        <v>2.2</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>['33', '90+2']</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>['22']</t>
+          <t>['13', '25', '45+2']</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.16</v>
+        <v>2.3</v>
       </c>
       <c r="AH48" t="n">
-        <v>2.04</v>
+        <v>1.12</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.51</v>
+        <v>2.65</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2.64</v>
+        <v>1.5</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45625.66666666666</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,22 +6706,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
         <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -6732,83 +6732,83 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.42</v>
+        <v>1.68</v>
       </c>
       <c r="M49" t="n">
-        <v>3.66</v>
+        <v>3.53</v>
       </c>
       <c r="N49" t="n">
-        <v>2.71</v>
+        <v>4.52</v>
       </c>
       <c r="O49" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="P49" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="R49" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S49" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T49" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U49" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="V49" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W49" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X49" t="n">
-        <v>4.33</v>
+        <v>4.65</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AD49" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>['58', '69']</t>
+          <t>['27']</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AJ49" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45625.66666666666</v>
@@ -6835,19 +6835,19 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G50" t="n">
         <v>2</v>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
         <v>2</v>
@@ -6861,52 +6861,52 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.53</v>
+        <v>1.81</v>
       </c>
       <c r="M50" t="n">
-        <v>3.46</v>
+        <v>3.9</v>
       </c>
       <c r="N50" t="n">
-        <v>2.69</v>
+        <v>3.98</v>
       </c>
       <c r="O50" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="P50" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="R50" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S50" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T50" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U50" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="V50" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W50" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X50" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AB50" t="n">
         <v>1.45</v>
@@ -6915,29 +6915,29 @@
         <v>1.57</v>
       </c>
       <c r="AD50" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>['7', '42']</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>['8']</t>
+        </is>
+      </c>
+      <c r="AG50" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ50" t="n">
         <v>2.35</v>
-      </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>['15', '32']</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>['45+1', '90+1']</t>
-        </is>
-      </c>
-      <c r="AG50" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>2</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45625.66666666666</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,22 +7222,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H53" t="n">
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -7248,83 +7248,83 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="M53" t="n">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="N53" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="O53" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="P53" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="R53" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S53" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T53" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U53" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="V53" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W53" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="X53" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="Y53" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC53" t="n">
         <v>1.75</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1.73</v>
       </c>
       <c r="AD53" t="n">
         <v>2</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25', '56', '85']</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.95</v>
+        <v>1.26</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.2</v>
+        <v>1.88</v>
       </c>
       <c r="AI53" t="n">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.57</v>
+        <v>2.63</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45625.6875</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,25 +7480,25 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -7506,83 +7506,83 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.75</v>
+        <v>3.3</v>
       </c>
       <c r="M55" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="N55" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="O55" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q55" t="n">
         <v>2.5</v>
       </c>
-      <c r="P55" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>4.5</v>
-      </c>
       <c r="R55" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T55" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U55" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V55" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W55" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X55" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AA55" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AD55" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>['25', '56', '85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>['90+1']</t>
+          <t>['45+1', '77']</t>
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.26</v>
+        <v>1.8</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.88</v>
+        <v>1.25</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AJ55" t="n">
-        <v>2.63</v>
+        <v>1.7</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45625.6875</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,25 +7609,25 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FeralpiSalò</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -7635,83 +7635,83 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="M56" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="N56" t="n">
-        <v>7</v>
+        <v>4.75</v>
       </c>
       <c r="O56" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="P56" t="n">
         <v>2.2</v>
       </c>
       <c r="Q56" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="R56" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S56" t="n">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="T56" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="U56" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="V56" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="W56" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X56" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>['1', '35', '39', '63', '70', '72']</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AI56" t="n">
         <v>1.44</v>
       </c>
-      <c r="X56" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>['75']</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>['10']</t>
-        </is>
-      </c>
-      <c r="AG56" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AJ56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45625.6875</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,25 +7738,25 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -7764,61 +7764,61 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="M57" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N57" t="n">
-        <v>2.15</v>
+        <v>5.4</v>
       </c>
       <c r="O57" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="P57" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.88</v>
+        <v>6</v>
       </c>
       <c r="R57" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="S57" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="T57" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="U57" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V57" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W57" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="X57" t="n">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AA57" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -7827,20 +7827,20 @@
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '48', '81']</t>
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.7</v>
+        <v>1.12</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.28</v>
+        <v>2.05</v>
       </c>
       <c r="AI57" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1.67</v>
+        <v>3.4</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45625.6875</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,109 +7867,109 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>FeralpiSalò</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M58" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N58" t="n">
+        <v>7</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P58" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X58" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y58" t="n">
         <v>2</v>
       </c>
-      <c r="H58" t="n">
-        <v>1</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L58" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="M58" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N58" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="O58" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P58" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R58" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S58" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T58" t="n">
-        <v>4</v>
-      </c>
-      <c r="U58" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V58" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W58" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X58" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>2.29</v>
-      </c>
       <c r="Z58" t="n">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="AA58" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="AG58" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AJ58" t="n">
         <v>5</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE58" t="inlineStr">
-        <is>
-          <t>['3', '35']</t>
-        </is>
-      </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>['79']</t>
-        </is>
-      </c>
-      <c r="AG58" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>1.91</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45625.6875</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,91 +7996,91 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M59" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N59" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O59" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P59" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S59" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T59" t="n">
         <v>3</v>
       </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="M59" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N59" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O59" t="n">
+      <c r="U59" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X59" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y59" t="n">
         <v>2.25</v>
       </c>
-      <c r="P59" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R59" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S59" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="T59" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U59" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V59" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W59" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X59" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y59" t="n">
+      <c r="Z59" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC59" t="n">
         <v>1.95</v>
       </c>
-      <c r="Z59" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AD59" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>['1', '35', '39', '63', '70', '72']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -8089,16 +8089,16 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.14</v>
+        <v>1.7</v>
       </c>
       <c r="AH59" t="n">
-        <v>2.11</v>
+        <v>1.28</v>
       </c>
       <c r="AI59" t="n">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="AJ59" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AK59" s="3" t="n">
         <v>45625.6875</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,25 +8125,25 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -8151,83 +8151,83 @@
         </is>
       </c>
       <c r="L60" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N60" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O60" t="n">
+        <v>4</v>
+      </c>
+      <c r="P60" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S60" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X60" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y60" t="n">
         <v>1.75</v>
       </c>
-      <c r="M60" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N60" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O60" t="n">
+      <c r="Z60" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="AG60" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI60" t="n">
         <v>2.5</v>
       </c>
-      <c r="P60" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>6</v>
-      </c>
-      <c r="R60" t="n">
+      <c r="AJ60" t="n">
         <v>1.57</v>
-      </c>
-      <c r="S60" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T60" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U60" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V60" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W60" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X60" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>['15', '48', '81']</t>
-        </is>
-      </c>
-      <c r="AG60" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>3.4</v>
       </c>
       <c r="AK60" s="3" t="n">
         <v>45625.6875</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,25 +8254,25 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H61" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" t="n">
         <v>2</v>
       </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -8280,83 +8280,83 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="M61" t="n">
-        <v>3.45</v>
+        <v>2.99</v>
       </c>
       <c r="N61" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O61" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S61" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X61" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC61" t="n">
         <v>2.1</v>
       </c>
-      <c r="O61" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P61" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R61" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S61" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T61" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V61" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W61" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X61" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Y61" t="n">
+      <c r="AD61" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>['3', '35']</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>['79']</t>
+        </is>
+      </c>
+      <c r="AG61" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ61" t="n">
         <v>1.91</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF61" t="inlineStr">
-        <is>
-          <t>['45+1', '77']</t>
-        </is>
-      </c>
-      <c r="AG61" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI61" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ61" t="n">
-        <v>1.7</v>
       </c>
       <c r="AK61" s="3" t="n">
         <v>45625.6875</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,16 +8770,16 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65" t="n">
         <v>1</v>
@@ -8788,7 +8788,7 @@
         <v>1</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -8796,83 +8796,83 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.52</v>
+        <v>2.05</v>
       </c>
       <c r="M65" t="n">
-        <v>4.15</v>
+        <v>2.97</v>
       </c>
       <c r="N65" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="O65" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q65" t="n">
         <v>5</v>
       </c>
-      <c r="O65" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P65" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q65" t="n">
+      <c r="R65" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S65" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T65" t="n">
+        <v>4</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X65" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA65" t="n">
         <v>6</v>
       </c>
-      <c r="R65" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S65" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T65" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X65" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AB65" t="n">
-        <v>1.6</v>
+        <v>1.13</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="AD65" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>['29']</t>
+          <t>['45+3', '81']</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AH65" t="n">
-        <v>2.94</v>
+        <v>1.8</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AJ65" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AK65" s="3" t="n">
         <v>45625.70833333334</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,22 +8899,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G66" t="n">
         <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -8925,83 +8925,83 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.01</v>
+        <v>1.52</v>
       </c>
       <c r="M66" t="n">
-        <v>3.65</v>
+        <v>4.15</v>
       </c>
       <c r="N66" t="n">
-        <v>3.55</v>
+        <v>5</v>
       </c>
       <c r="O66" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="P66" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="R66" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="S66" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="T66" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X66" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>['59']</t>
+        </is>
+      </c>
+      <c r="AG66" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AJ66" t="n">
         <v>3.4</v>
-      </c>
-      <c r="U66" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V66" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W66" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X66" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE66" t="inlineStr">
-        <is>
-          <t>['83']</t>
-        </is>
-      </c>
-      <c r="AF66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG66" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>2.6</v>
       </c>
       <c r="AK66" s="3" t="n">
         <v>45625.70833333334</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,109 +9028,109 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M67" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N67" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O67" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P67" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S67" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W67" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X67" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC67" t="n">
         <v>2</v>
       </c>
-      <c r="H67" t="n">
-        <v>1</v>
-      </c>
-      <c r="I67" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" t="n">
-        <v>1</v>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="M67" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="N67" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="O67" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P67" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>5</v>
-      </c>
-      <c r="R67" t="n">
+      <c r="AD67" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG67" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI67" t="n">
         <v>1.62</v>
       </c>
-      <c r="S67" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T67" t="n">
-        <v>4</v>
-      </c>
-      <c r="U67" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V67" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W67" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X67" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>['45+3', '81']</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>['32']</t>
-        </is>
-      </c>
-      <c r="AG67" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH67" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI67" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ67" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AK67" s="3" t="n">
         <v>45625.70833333334</v>
@@ -9415,16 +9415,16 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sol de América</t>
+          <t>Nacional Asunción</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sportivo Ameliano</t>
+          <t>Guaraní</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -9444,62 +9444,62 @@
         <v>2.45</v>
       </c>
       <c r="M70" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N70" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="O70" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P70" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="R70" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="S70" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="T70" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U70" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V70" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W70" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="X70" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AA70" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AC70" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -9508,16 +9508,16 @@
         </is>
       </c>
       <c r="AG70" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AJ70" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AK70" s="3" t="n">
         <v>45625.8125</v>
@@ -9673,16 +9673,16 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nacional Asunción</t>
+          <t>Sol de América</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Guaraní</t>
+          <t>Sportivo Ameliano</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -9702,80 +9702,80 @@
         <v>2.45</v>
       </c>
       <c r="M72" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N72" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="O72" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P72" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="R72" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S72" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W72" t="n">
         <v>1.5</v>
       </c>
-      <c r="S72" t="n">
+      <c r="X72" t="n">
         <v>2.4</v>
       </c>
-      <c r="T72" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U72" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V72" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W72" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X72" t="n">
-        <v>2.8</v>
-      </c>
       <c r="Y72" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Z72" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD72" t="n">
         <v>1.67</v>
       </c>
-      <c r="AA72" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD72" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AE72" t="inlineStr">
         <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG72" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH72" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AI72" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AJ72" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AK72" s="3" t="n">
         <v>45625.8125</v>
